--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-15T19:11:07+00:00</t>
+    <t>2026-01-16T14:21:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-16T14:21:16+00:00</t>
+    <t>2026-01-19T10:22:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:22:08+00:00</t>
+    <t>2026-01-20T10:13:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:13:19+00:00</t>
+    <t>2026-01-21T17:03:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T17:03:29+00:00</t>
+    <t>2026-01-22T09:24:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T09:24:15+00:00</t>
+    <t>2026-01-22T12:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T12:59:21+00:00</t>
+    <t>2026-01-22T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationrequest-planeintrag.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$134</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4573" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4982" uniqueCount="808">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T19:34:42+00:00</t>
+    <t>2026-01-26T15:48:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet einen Eintrag eines Medikationsplans eines ELGA Teilnehmers ab. 
+    <t>**Beschreibung:** Bildet einen Medikationsplaneintrag im Medikationsplan eines ELGA Teilnehmers ab. 
 Er enthält genau ein Arzneimittel und dessen Dosierung.
 Kann in weiterer Folge dazu dienen, eine geplante Abgabe zu erstellen (AtEmedMedicationRequestGeplanteAbgabe).</t>
   </si>
@@ -511,7 +511,7 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status des Medikationsplaneintrags (im Standardfall active oder complete): active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown</t>
+    <t>Status des Medikationsplaneintrags (im Standardfall active oder complete): active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown -&gt; entfernen: draft, unknown</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -1248,6 +1248,39 @@
     <t>ORC-16-Order Control Code Reason /RXE-27-Give Indication/RXO-20-Indication / RXD-21-Indication / RXG-22-Indication / RXA-19-Indication</t>
   </si>
   <si>
+    <t>MedicationRequest.reasonCode.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.system</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.version</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.code</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.display</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.coding.userSelected</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reasonCode.text</t>
+  </si>
+  <si>
     <t>MedicationRequest.reasonReference</t>
   </si>
   <si>
@@ -1335,7 +1368,7 @@
     <t>MedicationRequest.courseOfTherapyType</t>
   </si>
   <si>
-    <t>Gesamtmuster der Medikamentengabe (z.B. saisonal). Evtl. im Medikationsplaneintrag (dosageInstruction), paused soll im Status dokumentiert werden.</t>
+    <t>Gesamtmuster der Medikamentengabe (z.B. saisonal). Verwendung im Medikationsplaneintrag prüfen (dosageInstruction), paused soll im Status dokumentiert werden.</t>
   </si>
   <si>
     <t>The description of the overall patte3rn of the administration of the medication to the patient.</t>
@@ -2817,7 +2850,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO123"/>
+  <dimension ref="A1:AO134"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="67.0546875" customWidth="true" bestFit="true"/>
@@ -8123,7 +8156,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>392</v>
       </c>
@@ -8139,10 +8172,10 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -8151,17 +8184,15 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>393</v>
+        <v>196</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>382</v>
+        <v>197</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -8210,31 +8241,31 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>392</v>
+        <v>199</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>396</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>397</v>
+        <v>200</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>390</v>
+        <v>21</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -8242,21 +8273,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -8265,18 +8296,20 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>399</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>400</v>
+        <v>137</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -8313,19 +8346,19 @@
         <v>21</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>398</v>
+        <v>206</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8337,16 +8370,16 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>402</v>
+        <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -8357,10 +8390,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8368,10 +8401,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -8383,16 +8416,20 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>104</v>
+        <v>208</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>405</v>
+        <v>209</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -8440,7 +8477,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>404</v>
+        <v>214</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8461,21 +8498,21 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8495,16 +8532,16 @@
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>408</v>
+        <v>196</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>409</v>
+        <v>197</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>410</v>
+        <v>198</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8555,28 +8592,28 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>407</v>
+        <v>199</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>411</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>412</v>
+        <v>200</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -8587,21 +8624,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -8610,21 +8647,21 @@
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>414</v>
+        <v>137</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -8660,40 +8697,40 @@
         <v>21</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>413</v>
+        <v>206</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>417</v>
+        <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>418</v>
+        <v>200</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -8704,10 +8741,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8715,7 +8752,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>90</v>
@@ -8727,21 +8764,23 @@
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>420</v>
+        <v>274</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>421</v>
+        <v>275</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -8765,13 +8804,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>423</v>
+        <v>21</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>424</v>
+        <v>21</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -8789,7 +8828,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>419</v>
+        <v>278</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8810,21 +8849,21 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>425</v>
+        <v>279</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>426</v>
+        <v>398</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>426</v>
+        <v>398</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8835,7 +8874,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -8844,18 +8883,20 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>427</v>
+        <v>196</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>428</v>
+        <v>283</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8904,13 +8945,13 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>426</v>
+        <v>286</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -8919,27 +8960,27 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>430</v>
+        <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>431</v>
+        <v>287</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>21</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>432</v>
+        <v>399</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>432</v>
+        <v>399</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8947,10 +8988,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -8959,19 +9000,21 @@
         <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>433</v>
+        <v>110</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>434</v>
+        <v>291</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>435</v>
+        <v>292</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -9019,13 +9062,13 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>432</v>
+        <v>294</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
@@ -9034,27 +9077,27 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>436</v>
+        <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>437</v>
+        <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>438</v>
+        <v>295</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>21</v>
+        <v>296</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>439</v>
+        <v>400</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>439</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9062,10 +9105,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -9074,21 +9117,21 @@
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>440</v>
+        <v>196</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>441</v>
+        <v>299</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -9136,13 +9179,13 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>439</v>
+        <v>302</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
@@ -9151,27 +9194,27 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>444</v>
+        <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>445</v>
+        <v>303</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>446</v>
+        <v>401</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>446</v>
+        <v>401</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9191,19 +9234,23 @@
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>197</v>
+        <v>307</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
@@ -9251,7 +9298,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>199</v>
+        <v>311</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9263,7 +9310,7 @@
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
@@ -9272,32 +9319,32 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>200</v>
+        <v>312</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>21</v>
+        <v>313</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>447</v>
+        <v>402</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>447</v>
+        <v>402</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -9306,21 +9353,23 @@
         <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>137</v>
+        <v>218</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -9356,31 +9405,31 @@
         <v>21</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
@@ -9389,25 +9438,25 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>448</v>
+        <v>403</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>448</v>
+        <v>403</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9417,29 +9466,27 @@
         <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>136</v>
+        <v>404</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>450</v>
+        <v>382</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>451</v>
+        <v>405</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -9487,7 +9534,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>452</v>
+        <v>403</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9499,19 +9546,19 @@
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>21</v>
+        <v>407</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>133</v>
+        <v>408</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>21</v>
+        <v>390</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -9519,10 +9566,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9533,7 +9580,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -9545,18 +9592,16 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>454</v>
+        <v>410</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>455</v>
+        <v>411</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>456</v>
+        <v>412</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>457</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -9604,13 +9649,13 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>458</v>
+        <v>409</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
@@ -9619,27 +9664,27 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>21</v>
+        <v>413</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>459</v>
+        <v>414</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>460</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>461</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>461</v>
+        <v>415</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9650,7 +9695,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -9662,18 +9707,16 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>196</v>
+        <v>104</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>462</v>
+        <v>416</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>463</v>
+        <v>417</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>464</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9721,13 +9764,13 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>465</v>
+        <v>415</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
@@ -9742,21 +9785,21 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>459</v>
+        <v>414</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>467</v>
+        <v>418</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>467</v>
+        <v>418</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9767,7 +9810,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -9779,20 +9822,16 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>169</v>
+        <v>419</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>468</v>
+        <v>420</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -9816,13 +9855,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>472</v>
+        <v>21</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>473</v>
+        <v>21</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9840,7 +9879,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>474</v>
+        <v>418</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9855,27 +9894,27 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>459</v>
+        <v>423</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>475</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>476</v>
+        <v>424</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>476</v>
+        <v>424</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9886,7 +9925,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -9898,16 +9937,18 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>196</v>
+        <v>148</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>477</v>
+        <v>425</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>478</v>
+        <v>426</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -9955,7 +9996,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>479</v>
+        <v>424</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9970,27 +10011,27 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>459</v>
+        <v>429</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>475</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>480</v>
+        <v>430</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>480</v>
+        <v>430</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10010,23 +10051,21 @@
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>481</v>
+        <v>169</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>482</v>
+        <v>431</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>483</v>
+        <v>432</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -10050,13 +10089,13 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>21</v>
+        <v>435</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -10074,7 +10113,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>486</v>
+        <v>430</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10095,7 +10134,7 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>487</v>
+        <v>436</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -10106,10 +10145,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>488</v>
+        <v>437</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>488</v>
+        <v>437</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10120,7 +10159,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -10132,13 +10171,13 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>196</v>
+        <v>438</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>197</v>
+        <v>439</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>198</v>
+        <v>440</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10189,28 +10228,28 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>199</v>
+        <v>437</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>21</v>
+        <v>441</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>200</v>
+        <v>442</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -10221,14 +10260,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>489</v>
+        <v>443</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>489</v>
+        <v>443</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10247,17 +10286,15 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>136</v>
+        <v>444</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>137</v>
+        <v>445</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -10294,19 +10331,19 @@
         <v>21</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>206</v>
+        <v>443</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10318,16 +10355,16 @@
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>21</v>
+        <v>447</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>200</v>
+        <v>449</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -10338,14 +10375,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10358,26 +10395,24 @@
         <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>136</v>
+        <v>451</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -10425,7 +10460,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10437,16 +10472,16 @@
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>21</v>
+        <v>455</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>133</v>
+        <v>456</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -10457,10 +10492,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>491</v>
+        <v>457</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>491</v>
+        <v>457</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10471,7 +10506,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -10480,21 +10515,19 @@
         <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>346</v>
+        <v>196</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>492</v>
+        <v>197</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>493</v>
+        <v>198</v>
       </c>
       <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>494</v>
-      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -10542,19 +10575,19 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>495</v>
+        <v>199</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
@@ -10563,7 +10596,7 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>496</v>
+        <v>200</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -10574,21 +10607,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>497</v>
+        <v>458</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>497</v>
+        <v>458</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -10597,21 +10630,21 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>498</v>
+        <v>136</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>499</v>
+        <v>137</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -10647,31 +10680,31 @@
         <v>21</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>206</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>503</v>
+        <v>141</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>21</v>
@@ -10680,7 +10713,7 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>504</v>
+        <v>200</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -10691,42 +10724,46 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>505</v>
+        <v>459</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>505</v>
+        <v>459</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>21</v>
+        <v>460</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>197</v>
+        <v>461</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
@@ -10774,19 +10811,19 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>199</v>
+        <v>463</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
@@ -10795,7 +10832,7 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10806,21 +10843,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>506</v>
+        <v>464</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>506</v>
+        <v>464</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -10829,21 +10866,21 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>136</v>
+        <v>465</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>137</v>
+        <v>466</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>467</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -10879,31 +10916,31 @@
         <v>21</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>206</v>
+        <v>469</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
@@ -10912,21 +10949,21 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>200</v>
+        <v>470</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>507</v>
+        <v>472</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>507</v>
+        <v>472</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10949,16 +10986,18 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>508</v>
+        <v>196</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>509</v>
+        <v>473</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>510</v>
+        <v>474</v>
       </c>
       <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -11006,7 +11045,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>511</v>
+        <v>476</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11027,21 +11066,21 @@
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>512</v>
+        <v>470</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>21</v>
+        <v>477</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>513</v>
+        <v>478</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>513</v>
+        <v>478</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11052,7 +11091,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
@@ -11064,19 +11103,19 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>514</v>
+        <v>169</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>515</v>
+        <v>479</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>516</v>
+        <v>480</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>517</v>
+        <v>481</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>518</v>
+        <v>482</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -11101,13 +11140,13 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>21</v>
+        <v>483</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>21</v>
+        <v>484</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -11125,13 +11164,13 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>519</v>
+        <v>485</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
@@ -11146,21 +11185,21 @@
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>520</v>
+        <v>470</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>21</v>
+        <v>486</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>521</v>
+        <v>487</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>521</v>
+        <v>487</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11183,13 +11222,13 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>514</v>
+        <v>196</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>522</v>
+        <v>488</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>523</v>
+        <v>489</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11240,7 +11279,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>524</v>
+        <v>490</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11261,21 +11300,21 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>520</v>
+        <v>470</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>21</v>
+        <v>486</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>525</v>
+        <v>491</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>525</v>
+        <v>491</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11298,19 +11337,19 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>526</v>
+        <v>492</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>527</v>
+        <v>493</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>528</v>
+        <v>494</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>529</v>
+        <v>495</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>530</v>
+        <v>496</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -11359,7 +11398,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>531</v>
+        <v>497</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11380,7 +11419,7 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>532</v>
+        <v>498</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -11391,10 +11430,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>533</v>
+        <v>499</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>533</v>
+        <v>499</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11414,23 +11453,19 @@
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>526</v>
+        <v>196</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>534</v>
+        <v>197</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>21</v>
       </c>
@@ -11478,7 +11513,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>536</v>
+        <v>199</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11490,7 +11525,7 @@
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>21</v>
@@ -11499,7 +11534,7 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>532</v>
+        <v>200</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -11510,21 +11545,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -11533,18 +11568,20 @@
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>538</v>
+        <v>137</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -11569,43 +11606,43 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>540</v>
+        <v>21</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>541</v>
+        <v>21</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>542</v>
+        <v>206</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
@@ -11614,7 +11651,7 @@
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>543</v>
+        <v>200</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -11625,48 +11662,50 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>544</v>
+        <v>501</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>544</v>
+        <v>501</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>21</v>
+        <v>460</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>514</v>
+        <v>136</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>545</v>
+        <v>461</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q76" t="s" s="2">
-        <v>547</v>
-      </c>
+      <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
         <v>21</v>
       </c>
@@ -11710,19 +11749,19 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>548</v>
+        <v>463</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>21</v>
@@ -11731,7 +11770,7 @@
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>532</v>
+        <v>133</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -11742,10 +11781,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>549</v>
+        <v>502</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>549</v>
+        <v>502</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11756,7 +11795,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>21</v>
@@ -11768,16 +11807,18 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>514</v>
+        <v>346</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>550</v>
+        <v>503</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>551</v>
+        <v>504</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -11825,13 +11866,13 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>552</v>
+        <v>506</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
@@ -11846,7 +11887,7 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>532</v>
+        <v>507</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -11857,10 +11898,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>553</v>
+        <v>508</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>553</v>
+        <v>508</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11883,16 +11924,18 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>554</v>
+        <v>510</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>555</v>
+        <v>511</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -11940,7 +11983,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>556</v>
+        <v>513</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11952,7 +11995,7 @@
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>102</v>
+        <v>514</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>21</v>
@@ -11961,7 +12004,7 @@
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -11972,10 +12015,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>557</v>
+        <v>516</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>557</v>
+        <v>516</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11995,16 +12038,16 @@
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>526</v>
+        <v>196</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>558</v>
+        <v>197</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>559</v>
+        <v>198</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12055,7 +12098,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>560</v>
+        <v>199</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12067,7 +12110,7 @@
         <v>21</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>21</v>
@@ -12076,7 +12119,7 @@
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>532</v>
+        <v>200</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
@@ -12087,21 +12130,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>561</v>
+        <v>517</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>561</v>
+        <v>517</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>21</v>
@@ -12110,18 +12153,20 @@
         <v>21</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>562</v>
+        <v>137</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -12146,43 +12191,43 @@
         <v>21</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>540</v>
+        <v>21</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>541</v>
+        <v>21</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>564</v>
+        <v>206</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>21</v>
@@ -12191,7 +12236,7 @@
         <v>21</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>543</v>
+        <v>200</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -12202,10 +12247,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>565</v>
+        <v>518</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>565</v>
+        <v>518</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12216,7 +12261,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>21</v>
@@ -12228,17 +12273,15 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>110</v>
+        <v>519</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>566</v>
+        <v>520</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>568</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -12263,11 +12306,13 @@
         <v>21</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y81" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z81" t="s" s="2">
-        <v>569</v>
+        <v>21</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>21</v>
@@ -12285,13 +12330,13 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>570</v>
+        <v>522</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>21</v>
@@ -12306,7 +12351,7 @@
         <v>21</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>200</v>
+        <v>523</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -12317,10 +12362,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>571</v>
+        <v>524</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>571</v>
+        <v>524</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12331,7 +12376,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>21</v>
@@ -12343,18 +12388,20 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>572</v>
+        <v>525</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>573</v>
+        <v>526</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>574</v>
+        <v>527</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
       </c>
@@ -12402,13 +12449,13 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>576</v>
+        <v>530</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>21</v>
@@ -12423,7 +12470,7 @@
         <v>21</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>200</v>
+        <v>531</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
@@ -12434,10 +12481,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>577</v>
+        <v>532</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>577</v>
+        <v>532</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12448,7 +12495,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -12460,20 +12507,16 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>110</v>
+        <v>525</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>578</v>
+        <v>533</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>581</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>21</v>
       </c>
@@ -12497,11 +12540,13 @@
         <v>21</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z83" t="s" s="2">
-        <v>582</v>
+        <v>21</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>21</v>
@@ -12519,13 +12564,13 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>583</v>
+        <v>535</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
@@ -12540,7 +12585,7 @@
         <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>584</v>
+        <v>531</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -12551,10 +12596,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>585</v>
+        <v>536</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>585</v>
+        <v>536</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12577,16 +12622,20 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>586</v>
+        <v>537</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>587</v>
+        <v>538</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -12634,7 +12683,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>589</v>
+        <v>542</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12655,7 +12704,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>590</v>
+        <v>543</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -12666,10 +12715,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>591</v>
+        <v>544</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>591</v>
+        <v>544</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12692,18 +12741,20 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>169</v>
+        <v>537</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>592</v>
+        <v>545</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>593</v>
+        <v>546</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
       </c>
@@ -12727,13 +12778,13 @@
         <v>21</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>595</v>
+        <v>21</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>596</v>
+        <v>21</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>21</v>
@@ -12751,7 +12802,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>597</v>
+        <v>547</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12772,7 +12823,7 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>598</v>
+        <v>543</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12783,10 +12834,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>599</v>
+        <v>548</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>599</v>
+        <v>548</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12809,17 +12860,15 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>601</v>
+        <v>549</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>603</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -12844,13 +12893,13 @@
         <v>21</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>604</v>
+        <v>551</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>605</v>
+        <v>552</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>21</v>
@@ -12868,7 +12917,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>606</v>
+        <v>553</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12889,21 +12938,21 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>607</v>
+        <v>554</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>608</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12926,24 +12975,22 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>169</v>
+        <v>525</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>610</v>
+        <v>556</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q87" s="2"/>
+      <c r="Q87" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="R87" t="s" s="2">
         <v>21</v>
       </c>
@@ -12963,13 +13010,13 @@
         <v>21</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>614</v>
+        <v>21</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>615</v>
+        <v>21</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>21</v>
@@ -12987,7 +13034,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>616</v>
+        <v>559</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13008,21 +13055,21 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>617</v>
+        <v>543</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>618</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>619</v>
+        <v>560</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>619</v>
+        <v>560</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13045,18 +13092,16 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>169</v>
+        <v>525</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>620</v>
+        <v>561</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>621</v>
+        <v>562</v>
       </c>
       <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>622</v>
-      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>21</v>
       </c>
@@ -13080,13 +13125,13 @@
         <v>21</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>623</v>
+        <v>21</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>624</v>
+        <v>21</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>21</v>
@@ -13104,7 +13149,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>625</v>
+        <v>563</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13125,21 +13170,21 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>626</v>
+        <v>543</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>627</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>628</v>
+        <v>564</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>628</v>
+        <v>564</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13162,20 +13207,16 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>169</v>
+        <v>537</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>629</v>
+        <v>565</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>632</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>21</v>
       </c>
@@ -13199,13 +13240,13 @@
         <v>21</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>633</v>
+        <v>21</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>634</v>
+        <v>21</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>21</v>
@@ -13223,7 +13264,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>635</v>
+        <v>567</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13244,21 +13285,21 @@
         <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>636</v>
+        <v>543</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>637</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>638</v>
+        <v>568</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>638</v>
+        <v>568</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13269,7 +13310,7 @@
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>21</v>
@@ -13281,13 +13322,13 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>498</v>
+        <v>537</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>639</v>
+        <v>569</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>640</v>
+        <v>570</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13338,13 +13379,13 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>641</v>
+        <v>571</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>21</v>
@@ -13359,21 +13400,21 @@
         <v>21</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>21</v>
+        <v>543</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>642</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>643</v>
+        <v>572</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>643</v>
+        <v>572</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13393,16 +13434,16 @@
         <v>21</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>196</v>
+        <v>110</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>197</v>
+        <v>573</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>198</v>
+        <v>574</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13429,13 +13470,13 @@
         <v>21</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>21</v>
+        <v>551</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>21</v>
+        <v>552</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>21</v>
@@ -13453,7 +13494,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>199</v>
+        <v>575</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13465,7 +13506,7 @@
         <v>21</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>21</v>
@@ -13474,7 +13515,7 @@
         <v>21</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>200</v>
+        <v>554</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>21</v>
@@ -13485,14 +13526,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>644</v>
+        <v>576</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>644</v>
+        <v>576</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13508,19 +13549,19 @@
         <v>21</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>137</v>
+        <v>577</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>202</v>
+        <v>578</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>139</v>
+        <v>579</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13546,31 +13587,29 @@
         <v>21</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>21</v>
+        <v>580</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>206</v>
+        <v>581</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13582,7 +13621,7 @@
         <v>21</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>21</v>
@@ -13602,10 +13641,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>645</v>
+        <v>582</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>645</v>
+        <v>582</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13616,7 +13655,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>21</v>
@@ -13628,18 +13667,18 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>169</v>
+        <v>583</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>646</v>
+        <v>584</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" t="s" s="2">
-        <v>648</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>21</v>
       </c>
@@ -13663,13 +13702,13 @@
         <v>21</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>649</v>
+        <v>21</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>650</v>
+        <v>21</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>21</v>
@@ -13687,13 +13726,13 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>651</v>
+        <v>587</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>21</v>
@@ -13708,21 +13747,21 @@
         <v>21</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>652</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>653</v>
+        <v>588</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>653</v>
+        <v>588</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13733,7 +13772,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>21</v>
@@ -13745,19 +13784,19 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>654</v>
+        <v>110</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>655</v>
+        <v>589</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>656</v>
+        <v>590</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>657</v>
+        <v>591</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>658</v>
+        <v>592</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>21</v>
@@ -13782,13 +13821,11 @@
         <v>21</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>21</v>
+        <v>593</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>21</v>
@@ -13806,13 +13843,13 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>659</v>
+        <v>594</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>21</v>
@@ -13827,21 +13864,21 @@
         <v>21</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>636</v>
+        <v>595</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>660</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>661</v>
+        <v>596</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>661</v>
+        <v>596</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13852,7 +13889,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>21</v>
@@ -13864,20 +13901,16 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>662</v>
+        <v>597</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>663</v>
+        <v>598</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>666</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>21</v>
       </c>
@@ -13925,7 +13958,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>667</v>
+        <v>600</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13946,21 +13979,21 @@
         <v>21</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>668</v>
+        <v>601</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>669</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>670</v>
+        <v>602</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>670</v>
+        <v>602</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13983,20 +14016,18 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>671</v>
+        <v>169</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>672</v>
+        <v>603</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>673</v>
+        <v>604</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>675</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>21</v>
       </c>
@@ -14020,13 +14051,13 @@
         <v>21</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>21</v>
+        <v>606</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>21</v>
+        <v>607</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>21</v>
@@ -14044,7 +14075,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>676</v>
+        <v>608</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14065,21 +14096,21 @@
         <v>21</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>677</v>
+        <v>609</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>678</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>679</v>
+        <v>610</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>679</v>
+        <v>610</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14102,20 +14133,18 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>680</v>
+        <v>611</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>681</v>
+        <v>612</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>682</v>
+        <v>613</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>684</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>21</v>
       </c>
@@ -14139,13 +14168,13 @@
         <v>21</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>21</v>
+        <v>615</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>21</v>
+        <v>616</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>21</v>
@@ -14163,7 +14192,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>685</v>
+        <v>617</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14184,21 +14213,21 @@
         <v>21</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>686</v>
+        <v>618</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>21</v>
+        <v>619</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>687</v>
+        <v>620</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>687</v>
+        <v>620</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14221,17 +14250,19 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>680</v>
+        <v>169</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>688</v>
+        <v>621</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="O98" t="s" s="2">
-        <v>690</v>
+        <v>624</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>21</v>
@@ -14256,13 +14287,13 @@
         <v>21</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>21</v>
+        <v>625</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>21</v>
+        <v>626</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>21</v>
@@ -14280,7 +14311,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>691</v>
+        <v>627</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14301,21 +14332,21 @@
         <v>21</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>686</v>
+        <v>628</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>21</v>
+        <v>629</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>692</v>
+        <v>630</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>692</v>
+        <v>630</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14335,19 +14366,21 @@
         <v>21</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>693</v>
+        <v>169</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>694</v>
+        <v>631</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>695</v>
+        <v>632</v>
       </c>
       <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
       </c>
@@ -14371,13 +14404,13 @@
         <v>21</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>21</v>
+        <v>634</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>21</v>
+        <v>635</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>21</v>
@@ -14395,7 +14428,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>692</v>
+        <v>636</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14413,24 +14446,24 @@
         <v>21</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>696</v>
+        <v>21</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>697</v>
+        <v>637</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>21</v>
+        <v>638</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>698</v>
+        <v>639</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>698</v>
+        <v>639</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14450,19 +14483,23 @@
         <v>21</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>197</v>
+        <v>640</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>641</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>21</v>
       </c>
@@ -14486,13 +14523,13 @@
         <v>21</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>21</v>
+        <v>644</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>21</v>
+        <v>645</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>21</v>
@@ -14510,7 +14547,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>199</v>
+        <v>646</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14522,7 +14559,7 @@
         <v>21</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>21</v>
@@ -14531,25 +14568,25 @@
         <v>21</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>200</v>
+        <v>647</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>21</v>
+        <v>648</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>699</v>
+        <v>649</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>699</v>
+        <v>649</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14565,20 +14602,18 @@
         <v>21</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>136</v>
+        <v>509</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>137</v>
+        <v>650</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14627,7 +14662,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>206</v>
+        <v>652</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14639,7 +14674,7 @@
         <v>21</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>21</v>
@@ -14648,57 +14683,53 @@
         <v>21</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>21</v>
+        <v>653</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>700</v>
+        <v>654</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>700</v>
+        <v>654</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>450</v>
+        <v>197</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>21</v>
       </c>
@@ -14746,19 +14777,19 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>452</v>
+        <v>199</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>21</v>
@@ -14767,7 +14798,7 @@
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>21</v>
@@ -14778,21 +14809,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>701</v>
+        <v>655</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>701</v>
+        <v>655</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>21</v>
@@ -14804,16 +14835,16 @@
         <v>21</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>693</v>
+        <v>136</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>702</v>
+        <v>137</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>703</v>
+        <v>202</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>704</v>
+        <v>139</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14851,31 +14882,31 @@
         <v>21</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>701</v>
+        <v>206</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>21</v>
@@ -14884,7 +14915,7 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>705</v>
+        <v>200</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>21</v>
@@ -14895,10 +14926,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>706</v>
+        <v>656</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>706</v>
+        <v>656</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14918,19 +14949,21 @@
         <v>21</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>197</v>
+        <v>657</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>198</v>
+        <v>658</v>
       </c>
       <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+      <c r="O104" t="s" s="2">
+        <v>659</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
       </c>
@@ -14954,13 +14987,13 @@
         <v>21</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>21</v>
+        <v>660</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>21</v>
+        <v>661</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>21</v>
@@ -14978,7 +15011,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>199</v>
+        <v>662</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14990,7 +15023,7 @@
         <v>21</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>21</v>
@@ -14999,32 +15032,32 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>21</v>
+        <v>663</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>707</v>
+        <v>664</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>707</v>
+        <v>664</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>21</v>
@@ -15033,21 +15066,23 @@
         <v>21</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>136</v>
+        <v>665</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>137</v>
+        <v>666</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>202</v>
+        <v>667</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>668</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>669</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>21</v>
       </c>
@@ -15095,19 +15130,19 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>206</v>
+        <v>670</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>21</v>
@@ -15116,56 +15151,56 @@
         <v>21</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>200</v>
+        <v>647</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>21</v>
+        <v>671</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>708</v>
+        <v>672</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>708</v>
+        <v>672</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>136</v>
+        <v>673</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>450</v>
+        <v>674</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>451</v>
+        <v>675</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>139</v>
+        <v>676</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>145</v>
+        <v>677</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>21</v>
@@ -15214,19 +15249,19 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>452</v>
+        <v>678</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>21</v>
@@ -15235,21 +15270,21 @@
         <v>21</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>133</v>
+        <v>679</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>21</v>
+        <v>680</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>709</v>
+        <v>681</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>709</v>
+        <v>681</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15269,19 +15304,23 @@
         <v>21</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>710</v>
+        <v>683</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>684</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>686</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
       </c>
@@ -15329,7 +15368,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>709</v>
+        <v>687</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15350,21 +15389,21 @@
         <v>21</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>712</v>
+        <v>688</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>21</v>
+        <v>689</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>713</v>
+        <v>690</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>713</v>
+        <v>690</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15384,19 +15423,23 @@
         <v>21</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>714</v>
+        <v>691</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>715</v>
+        <v>692</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+        <v>693</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>695</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>21</v>
       </c>
@@ -15444,7 +15487,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>713</v>
+        <v>696</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15465,7 +15508,7 @@
         <v>21</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>717</v>
+        <v>697</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>21</v>
@@ -15476,10 +15519,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>718</v>
+        <v>698</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>718</v>
+        <v>698</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15499,19 +15542,21 @@
         <v>21</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>714</v>
+        <v>691</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>719</v>
+        <v>699</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+      <c r="O109" t="s" s="2">
+        <v>701</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>21</v>
       </c>
@@ -15559,7 +15604,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15580,7 +15625,7 @@
         <v>21</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>717</v>
+        <v>697</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>21</v>
@@ -15591,10 +15636,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15617,20 +15662,16 @@
         <v>21</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>722</v>
+        <v>704</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>723</v>
+        <v>705</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>726</v>
-      </c>
+        <v>706</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>21</v>
       </c>
@@ -15678,7 +15719,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15696,10 +15737,10 @@
         <v>21</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>727</v>
+        <v>707</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>728</v>
+        <v>708</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>21</v>
@@ -15710,10 +15751,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>729</v>
+        <v>709</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>729</v>
+        <v>709</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15736,17 +15777,15 @@
         <v>21</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>586</v>
+        <v>196</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>730</v>
+        <v>197</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>732</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>21</v>
@@ -15795,7 +15834,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>729</v>
+        <v>199</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15807,41 +15846,41 @@
         <v>21</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>733</v>
+        <v>21</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>734</v>
+        <v>200</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>735</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>736</v>
+        <v>710</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>736</v>
+        <v>710</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>21</v>
@@ -15853,15 +15892,17 @@
         <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>680</v>
+        <v>136</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>737</v>
+        <v>137</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>21</v>
@@ -15910,76 +15951,78 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>736</v>
+        <v>206</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>739</v>
+        <v>21</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>740</v>
+        <v>200</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>741</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>742</v>
+        <v>711</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>742</v>
+        <v>711</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>21</v>
+        <v>460</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>714</v>
+        <v>136</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>743</v>
+        <v>461</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>744</v>
+        <v>462</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
       </c>
@@ -16027,28 +16070,28 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>742</v>
+        <v>463</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>746</v>
+        <v>21</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>747</v>
+        <v>133</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>21</v>
@@ -16059,10 +16102,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>748</v>
+        <v>712</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>748</v>
+        <v>712</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16085,15 +16128,17 @@
         <v>21</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>749</v>
+        <v>704</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>750</v>
+        <v>713</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>714</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>715</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>21</v>
@@ -16142,7 +16187,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>748</v>
+        <v>712</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16163,10 +16208,10 @@
         <v>21</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>752</v>
+        <v>716</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>21</v>
@@ -16174,10 +16219,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>753</v>
+        <v>717</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>753</v>
+        <v>717</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16200,13 +16245,13 @@
         <v>21</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>693</v>
+        <v>196</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>754</v>
+        <v>197</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>755</v>
+        <v>198</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16257,7 +16302,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>753</v>
+        <v>199</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16269,16 +16314,16 @@
         <v>21</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>756</v>
+        <v>21</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>757</v>
+        <v>200</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>21</v>
@@ -16289,21 +16334,21 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>758</v>
+        <v>718</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>758</v>
+        <v>718</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>21</v>
@@ -16315,15 +16360,17 @@
         <v>21</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N116" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>21</v>
@@ -16372,19 +16419,19 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>21</v>
@@ -16404,14 +16451,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>759</v>
+        <v>719</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>759</v>
+        <v>719</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>135</v>
+        <v>460</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16424,24 +16471,26 @@
         <v>21</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>137</v>
+        <v>461</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>202</v>
+        <v>462</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="O117" s="2"/>
+      <c r="O117" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>21</v>
       </c>
@@ -16489,7 +16538,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>206</v>
+        <v>463</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16510,7 +16559,7 @@
         <v>21</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>21</v>
@@ -16521,46 +16570,42 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>760</v>
+        <v>720</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>760</v>
+        <v>720</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>136</v>
+        <v>691</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>450</v>
+        <v>721</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>722</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>21</v>
       </c>
@@ -16608,19 +16653,19 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>452</v>
+        <v>720</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>21</v>
@@ -16629,7 +16674,7 @@
         <v>21</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>133</v>
+        <v>723</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>21</v>
@@ -16640,10 +16685,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>761</v>
+        <v>724</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>761</v>
+        <v>724</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16651,7 +16696,7 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>90</v>
@@ -16666,17 +16711,15 @@
         <v>21</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>762</v>
+        <v>726</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>764</v>
-      </c>
+        <v>727</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>21</v>
@@ -16701,13 +16744,13 @@
         <v>21</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>765</v>
+        <v>21</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>766</v>
+        <v>21</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>21</v>
@@ -16725,10 +16768,10 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>761</v>
+        <v>724</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>90</v>
@@ -16743,24 +16786,24 @@
         <v>21</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>756</v>
+        <v>21</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>767</v>
+        <v>728</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>768</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>769</v>
+        <v>729</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>769</v>
+        <v>729</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16783,13 +16826,13 @@
         <v>21</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>169</v>
+        <v>725</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>770</v>
+        <v>730</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>771</v>
+        <v>731</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16816,13 +16859,13 @@
         <v>21</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>772</v>
+        <v>21</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>773</v>
+        <v>21</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>21</v>
@@ -16840,7 +16883,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>769</v>
+        <v>729</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16858,24 +16901,24 @@
         <v>21</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>774</v>
+        <v>21</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>775</v>
+        <v>728</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>776</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>777</v>
+        <v>732</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>777</v>
+        <v>732</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16898,16 +16941,20 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>778</v>
+        <v>733</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>779</v>
+        <v>734</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
+        <v>735</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>737</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>21</v>
       </c>
@@ -16955,7 +17002,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>777</v>
+        <v>732</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16970,13 +17017,13 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>781</v>
+        <v>21</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>774</v>
+        <v>738</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>782</v>
+        <v>739</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>21</v>
@@ -16987,21 +17034,21 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>783</v>
+        <v>740</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>783</v>
+        <v>740</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>784</v>
+        <v>21</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>21</v>
@@ -17013,16 +17060,16 @@
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>785</v>
+        <v>597</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>786</v>
+        <v>741</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>787</v>
+        <v>742</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>788</v>
+        <v>743</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17072,13 +17119,13 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>783</v>
+        <v>740</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>21</v>
@@ -17090,24 +17137,24 @@
         <v>21</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>21</v>
+        <v>744</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>789</v>
+        <v>745</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>21</v>
+        <v>746</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>790</v>
+        <v>747</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>790</v>
+        <v>747</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17118,7 +17165,7 @@
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>21</v>
@@ -17130,17 +17177,15 @@
         <v>21</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>791</v>
+        <v>691</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>792</v>
+        <v>748</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>794</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>21</v>
@@ -17189,13 +17234,13 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>790</v>
+        <v>747</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>21</v>
@@ -17204,23 +17249,1302 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
         <v>795</v>
       </c>
-      <c r="AL123" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM123" t="s" s="2">
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K133" t="s" s="2">
         <v>796</v>
       </c>
-      <c r="AN123" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO123" t="s" s="2">
+      <c r="L133" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO134" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO123">
+  <autoFilter ref="A1:AO134">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17230,7 +18554,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI122">
+  <conditionalFormatting sqref="A2:AI133">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
